--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487862_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487862_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.686400000000001</v>
+        <v>6.6745</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9876</v>
+        <v>7.4455</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3012</v>
+        <v>-0.7709</v>
       </c>
       <c r="G2" t="n">
         <v>4.0576</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4207</v>
+        <v>2.4088</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2176</v>
+        <v>1.6755</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2031</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3659</v>
+        <v>2.9169</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6279</v>
+        <v>5.9551</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.262</v>
+        <v>-3.0382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9091</v>
+        <v>3.8869</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1024</v>
+        <v>-0.7185</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8066</v>
+        <v>4.6054</v>
       </c>
       <c r="J3" t="n">
-        <v>2.044</v>
+        <v>7.9448</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6332</v>
+        <v>1.2044</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4108</v>
+        <v>6.7404</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1349</v>
+        <v>-4.0579</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5308</v>
+        <v>-1.923</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6041</v>
+        <v>-2.1349</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6244</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8325</v>
+        <v>1.3193</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5839</v>
+        <v>1.1321</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2486</v>
+        <v>0.1873</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2532</v>
+        <v>2.6873</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4968</v>
+        <v>2.9493</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.2437</v>
+        <v>-0.262</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8869</v>
+        <v>0.9091</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7185</v>
+        <v>0.1024</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6054</v>
+        <v>0.8066</v>
       </c>
       <c r="J4" t="n">
-        <v>7.9448</v>
+        <v>2.044</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2044</v>
+        <v>0.6332</v>
       </c>
       <c r="L4" t="n">
-        <v>6.7404</v>
+        <v>1.4108</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0579</v>
+        <v>-1.1349</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.923</v>
+        <v>-0.5308</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1349</v>
+        <v>-0.6041</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2893</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3445</v>
+        <v>1.1539</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3262</v>
+        <v>0.9054</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0183</v>
+        <v>0.2486</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5613</v>
+        <v>0.2757</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8582</v>
+        <v>2.602</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2969</v>
+        <v>-2.3263</v>
       </c>
       <c r="G5" t="n">
         <v>-3.087</v>
@@ -844,13 +844,13 @@
         <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8783</v>
+        <v>1.5927</v>
       </c>
       <c r="T5" t="n">
-        <v>1.646</v>
+        <v>1.3897</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2323</v>
+        <v>0.203</v>
       </c>
       <c r="V5" t="n">
         <v>0.9376</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0028</v>
+        <v>-1.2116</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9945000000000001</v>
+        <v>-0.8197</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9973</v>
+        <v>-0.392</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6186</v>
+        <v>-2.3354</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3368</v>
+        <v>-0.3327</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2818</v>
+        <v>-2.0027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6716</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6716</v>
+        <v>0.0104</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.9373</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2902</v>
+        <v>-1.4085</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0084</v>
+        <v>-0.3431</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2818</v>
+        <v>-1.0654</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2402</v>
+        <v>0.6888</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3635</v>
+        <v>0.8773</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1233</v>
+        <v>-0.1885</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.569</v>
+        <v>-1.7654</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2064</v>
+        <v>0.2025</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3626</v>
+        <v>-1.9679</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3354</v>
+        <v>-1.6186</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3327</v>
+        <v>-0.3368</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0027</v>
+        <v>-1.2818</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9268999999999999</v>
+        <v>0.6716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0104</v>
+        <v>0.6716</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9373</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4085</v>
+        <v>-2.2902</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3431</v>
+        <v>-1.0084</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0654</v>
+        <v>-1.2818</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3314</v>
+        <v>0.4776</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4906</v>
+        <v>0.5715</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1591</v>
+        <v>-0.0939</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8137</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2742</v>
+        <v>-2.1238</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-0.1396</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3291</v>
+        <v>-1.9841</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0698</v>
+        <v>-1.5517</v>
       </c>
       <c r="H8" t="n">
-        <v>0.341</v>
+        <v>-0.7312</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4108</v>
+        <v>-0.8205</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3509</v>
+        <v>-0.3882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4473</v>
+        <v>0.3262</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0963</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4207</v>
+        <v>-1.1636</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1063</v>
+        <v>-1.0574</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3144</v>
+        <v>-0.1061</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8731</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.538</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6687</v>
+        <v>-0.2182</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0745</v>
+        <v>0.0186</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4057</v>
+        <v>-0.2368</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4327</v>
+        <v>-2.501</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4192</v>
+        <v>-1.2013</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0135</v>
+        <v>-1.2997</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5517</v>
+        <v>-1.0698</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7312</v>
+        <v>0.341</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8205</v>
+        <v>-1.4108</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3882</v>
+        <v>0.3509</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3262</v>
+        <v>0.4473</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7144</v>
+        <v>-0.0963</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1636</v>
+        <v>-1.4207</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0574</v>
+        <v>-0.1063</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1061</v>
+        <v>-1.3144</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.538</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5271</v>
+        <v>0.4418</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.261</v>
+        <v>0.8182</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2662</v>
+        <v>-0.3764</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2609</v>
+        <v>-2.9916</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6281</v>
+        <v>1.4758</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6329</v>
+        <v>-4.4674</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1829</v>
+        <v>-3.7071</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4775</v>
+        <v>-1.6717</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7054</v>
+        <v>-2.0353</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2928</v>
+        <v>0.4325</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.1284</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.636</v>
+        <v>0.5609</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8901</v>
+        <v>-4.1396</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8207</v>
+        <v>-1.5434</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0694</v>
+        <v>-2.5962</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2081</v>
+        <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0458</v>
+        <v>0.8612</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2454</v>
+        <v>1.4783</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1996</v>
+        <v>-0.6171</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2914</v>
+        <v>-0.3538</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4599</v>
+        <v>0.8137</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7513</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5735</v>
+        <v>-3.4394</v>
       </c>
       <c r="E11" t="n">
-        <v>0.982</v>
+        <v>-0.7771</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5555</v>
+        <v>-2.6622</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7071</v>
+        <v>-2.1829</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6717</v>
+        <v>-1.4775</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0353</v>
+        <v>-0.7054</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4325</v>
+        <v>-1.2928</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1284</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5609</v>
+        <v>-0.636</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.1396</v>
+        <v>-0.8901</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5434</v>
+        <v>-0.8207</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5962</v>
+        <v>-0.0694</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.8325</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.2081</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.2487</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.4568</v>
-      </c>
       <c r="S11" t="n">
-        <v>0.2792</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9844000000000001</v>
+        <v>1.0963</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7052</v>
+        <v>-0.229</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3538</v>
+        <v>-1.2914</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8137</v>
+        <v>0.4599</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1675</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1226</v>
+        <v>-5.2382</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5765</v>
+        <v>-1.8683</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5461</v>
+        <v>-3.3699</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0161</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7665999999999999</v>
+        <v>1.6509</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8663</v>
+        <v>1.5745</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0998</v>
+        <v>0.0764</v>
       </c>
       <c r="V12" t="n">
         <v>-1.1675</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.368899999999998</v>
+        <v>-6.7166</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1717</v>
+        <v>15.8242</v>
       </c>
       <c r="F13" t="n">
-        <v>-22.5408</v>
+        <v>-22.5406</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.715000000000002</v>
+        <v>-9.715</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.162999999999999</v>
+        <v>-1.163</v>
       </c>
       <c r="I13" t="n">
         <v>-8.552099999999999</v>
@@ -1447,7 +1447,7 @@
         <v>8.9834</v>
       </c>
       <c r="L13" t="n">
-        <v>8.694900000000002</v>
+        <v>8.694900000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-27.3933</v>
@@ -1468,13 +1468,13 @@
         <v>12.487</v>
       </c>
       <c r="S13" t="n">
-        <v>10.5918</v>
+        <v>11.2442</v>
       </c>
       <c r="T13" t="n">
-        <v>10.885</v>
+        <v>11.5374</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2932</v>
+        <v>-0.2929999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0426</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2255</v>
+        <v>6.8239</v>
       </c>
       <c r="E14" t="n">
-        <v>6.726</v>
+        <v>6.8331</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="G14" t="n">
         <v>5.8593</v>
@@ -1546,13 +1546,13 @@
         <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5932</v>
+        <v>-0.9948</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3667</v>
+        <v>-0.2595</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2265</v>
+        <v>-0.7352</v>
       </c>
       <c r="V14" t="n">
         <v>1.7513</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1494</v>
+        <v>5.8701</v>
       </c>
       <c r="E15" t="n">
-        <v>9.854799999999999</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.7053</v>
+        <v>-3.4489</v>
       </c>
       <c r="G15" t="n">
         <v>2.9391</v>
@@ -1624,13 +1624,13 @@
         <v>2.9137</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6439</v>
+        <v>-0.9233</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8787</v>
+        <v>0.3429</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5227</v>
+        <v>-1.2663</v>
       </c>
       <c r="V15" t="n">
         <v>1.9813</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9814</v>
+        <v>5.8132</v>
       </c>
       <c r="E16" t="n">
-        <v>7.1339</v>
+        <v>7.5625</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1524</v>
+        <v>-1.7492</v>
       </c>
       <c r="G16" t="n">
         <v>2.785</v>
@@ -1702,13 +1702,13 @@
         <v>3.1218</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0929</v>
+        <v>-1.2611</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4195</v>
+        <v>0.0091</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6734</v>
+        <v>-1.2702</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5155</v>
+        <v>-0.2146</v>
       </c>
       <c r="E17" t="n">
-        <v>3.201</v>
+        <v>2.7724</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6856</v>
+        <v>-2.987</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0099</v>
@@ -1780,13 +1780,13 @@
         <v>2.9137</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3477</v>
+        <v>-1.0778</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5525</v>
+        <v>0.1239</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9002</v>
+        <v>-1.2016</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6296</v>
+        <v>-0.3541</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.018</v>
+        <v>-0.9109</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3884</v>
+        <v>0.5568</v>
       </c>
       <c r="G18" t="n">
         <v>0.9363</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9603</v>
+        <v>-0.6848</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.171</v>
+        <v>-0.0638</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7894</v>
+        <v>-0.6211</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8137</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8504</v>
+        <v>-0.8861</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5828</v>
+        <v>-0.9043</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2676</v>
+        <v>0.0181</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3471</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2734</v>
+        <v>-0.3091</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4782</v>
+        <v>0.1567</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.4658</v>
       </c>
       <c r="V19" t="n">
         <v>-0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9851</v>
+        <v>-1.2183</v>
       </c>
       <c r="E20" t="n">
-        <v>1.297</v>
+        <v>1.8328</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2821</v>
+        <v>-3.0512</v>
       </c>
       <c r="G20" t="n">
         <v>0.35</v>
@@ -2014,13 +2014,13 @@
         <v>2.2893</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7086</v>
+        <v>-0.9419</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3667</v>
+        <v>0.1691</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.342</v>
+        <v>-1.111</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8751</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2315</v>
+        <v>-2.1728</v>
       </c>
       <c r="E21" t="n">
         <v>-1.1779</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0536</v>
+        <v>-0.9948</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2886</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4423</v>
+        <v>-0.3836</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4599</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8064</v>
+        <v>-4.1492</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8933</v>
+        <v>-2.7862</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.913</v>
+        <v>-1.363</v>
       </c>
       <c r="G22" t="n">
         <v>-1.509</v>
@@ -2170,13 +2170,13 @@
         <v>2.9137</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5294</v>
+        <v>-1.8722</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.0105</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.4328</v>
+        <v>-1.8828</v>
       </c>
       <c r="V22" t="n">
         <v>1.5213</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.3688</v>
+        <v>9.5121</v>
       </c>
       <c r="E23" t="n">
-        <v>22.5407</v>
+        <v>22.5405</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.1717</v>
+        <v>-13.0284</v>
       </c>
       <c r="G23" t="n">
         <v>9.7151</v>
@@ -2248,13 +2248,13 @@
         <v>17.6902</v>
       </c>
       <c r="S23" t="n">
-        <v>-10.5917</v>
+        <v>-8.448599999999999</v>
       </c>
       <c r="T23" t="n">
         <v>0.2932</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.8851</v>
+        <v>-8.741899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>3.0427</v>
